--- a/extenbooks/ES1501.xlsx
+++ b/extenbooks/ES1501.xlsx
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -989,7 +989,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t># ES1501 — Working Class Unproductive Labor (Mohun 2013) — PENDING</t>
+          <t># ES1501 — Working Class Unproductive Labor (Mohun 2013)</t>
         </is>
       </c>
     </row>
@@ -1001,87 +1001,103 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>**Chapter**: External study</t>
+          <t>**Chapter**: External study — Mohun (2013). **Status**: book_period_validated. **Period**: 1948-1989. **Units**: thousands of workers.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Status**: pending_data_assembly</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>## Why pending</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Unproductive workers in the *working class* component of total unproductive labor (excluding managerial/supervisory). Mohun's 2013 RRPE paper decomposes total Lu into Working Class (Luw) and Managerial (Lum) categories.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Mohun decomposition CSVs</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>## Source</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>## Activation path</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>`data/source/external_studies/Mohun_unproductive_decomposition_1948_1989.csv`, column `Luw_mohun`. 1948=6,426K; 1989=24,674K.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Load from mohun_unproductive_decomposition_1948_1989.csv (working-class column)</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>## Citation</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mohun, Simon. 2013. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion (pending stub).*</t>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>*Generated by anu-ingestion.*</t>
         </is>
       </c>
     </row>

--- a/extenbooks/ES1501.xlsx
+++ b/extenbooks/ES1501.xlsx
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -876,7 +876,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Study 6</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948–1989</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -978,124 +978,161 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ES1501-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mohun 2013 RRPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># ES1501 — Working Class Unproductive Labor (Mohun 2013)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: External study — Mohun (2013). **Status**: book_period_validated. **Period**: 1948-1989. **Units**: thousands of workers.</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t># ES1501 — Working Class Unproductive Labor (Mohun 2013)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Unproductive workers in the *working class* component of total unproductive labor (excluding managerial/supervisory). Mohun's 2013 RRPE paper decomposes total Lu into Working Class (Luw) and Managerial (Lum) categories.</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>**Chapter**: External study — Mohun (2013). **Status**: book_period_validated. **Period**: 1948-1989. **Units**: thousands of workers.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>## Source</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>`data/source/external_studies/Mohun_unproductive_decomposition_1948_1989.csv`, column `Luw_mohun`. 1948=6,426K; 1989=24,674K.</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unproductive workers in the *working class* component of total unproductive labor (excluding managerial/supervisory). Mohun's 2013 RRPE paper decomposes total Lu into Working Class (Luw) and Managerial (Lum) categories.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>## Citation</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>## Source</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Mohun, Simon. 2013. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379.</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>`data/source/external_studies/Mohun_unproductive_decomposition_1948_1989.csv`, column `Luw_mohun`. 1948=6,426K; 1989=24,674K.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>## Citation</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Mohun, Simon. 2013. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
         </is>
@@ -1112,12 +1149,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="59" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1140,163 +1177,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Working class unproductive labor = unproductive workers who are members of the working class (i.e., whose work is controlled by others, who have no supervisory responsibilities above shop-floor level). Defined by location in the circuit of capital: these workers are involved in M→C or C'→M' transformations (purchasing inputs, selling outputs, financial, commercial, legal, business service activities) but are NOT supervisors. Identified via the BLS CES production worker / nonsupervisory worker criterion: the CES ratio of production workers to all workers is applied to NIPA full-time equivalents by sector, yielding working class employment. Unproductive working class = working class total minus productive working class.</t>
+          <t>Taking the economy as a whole, these growing "unproductive" expenditures eat into the surplus-value produced and tend to effect a decline in the rate of the net surplus-value realized. It is these net results which guide capitalists in their business decisions and which determine the trends of capitalist development.... (Gillman 1957: 85)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 3 and Appendix; full_transcription.md</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>empirical_values</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unproductive working class employment share of total employment: 1964 = 25.1%; peak 2007 = 30.0%; 2010 = ~29%. Trend: increased by about a fifth over 47 years. Unproductive working class wage share of total wages: 1964 = 18.6%; fell to 16.7% by 1992; rose back to 18.1% by 2010. Key finding: unlike total unproductive employment (which rose), the unproductive working class WAGE share is approximately flat and considerably lower than the employment share — a completely different pattern from supervisory wages.</t>
+          <t>Any laboring activity involved in these "metamorphoses" of capital (M – C and C' – M') adds no new value, and is unproductive. Only the wage-labor involved in the transformation of productive capital into commodity capital is productive.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 4.1, Fig 2; full_transcription.md</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>burden_finding</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Critical empirical finding: the unproductive working class absorbed 12.9% of money value added in 1964 and still 12.9% in 2010. Mean = 12.8%, standard deviation = 0.34 percentage points. Mohun concludes: 'Hence the burden to accumulation posed by the unproductive working class did not change over the whole period of 46 years.' This directly contradicts the received view (Moseley 1991, Paitaridis and Tsoulfidis 2012) that rising unproductive labor constitutes a growing burden on accumulation.</t>
+          <t>Separating "pure" organization from authoritarian hierarchy and supervision is both theoretically doubtful and empirically impossible. The labor involved in such activities is conventionally treated as unproductive, and the same practice is followed here.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 5, Fig 4; full_transcription.md</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>class_composition</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Working class = ~81.3% of employed population (average 1964-2010, standard deviation 0.88). Supervisors (managers-plus-capitalists) = ~18.7% of employed population. Class proportions remained remarkably stable over the 47-year period. The working class is divided into productive and unproductive components by location in the circuit of capital. Unproductive working class employment = ~25.1-30% of total employment; productive working class = ~52-58% of total employment.</t>
+          <t>Use the CES ratio of production workers to all workers for "Private industry"; for "Services" (1964-98); for "Logging"; for "Services" (1964-98) and for "Private service providing" (1998-2010).</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 3; full_transcription.md</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>construction_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Series registry construction: step 1 op=derive, formula='Lu × 0.813', inputs=['Mohun Lu'], output='ES1501-COMBINED'. This reflects the stable 81.3% working class share of total unproductive employment. Units: thousands of full-time equivalent employees. Period 1964-2010.</t>
+          <t>In this paper, "wages" means total compensation of employees (the sum of wage and salary accruals and employer-financed benefits). Where the meaning is restricted to accruals only, this is explicitly stated.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Series registry ES1501; Mohun_2013, Section 3</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>data_sources</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Primary data: BLS CES (Current Employment Statistics, both NAICS-based 1998-2010 and discontinued SIC-based 1964-1997); NIPA (BEA). Construction follows Shaikh and Tonak (1994) as revised by Mohun (2005). Working class employment: CES production worker ratio applied to NIPA ftes. Supervisory employment and wages: computed by subtraction (NIPA totals minus working class totals), which allocates all wages missing from CES — including stock options, bonuses, retroactive pay — to supervisory workers.</t>
+          <t>Hence: The NIPA data for "Private Industries" must be adjusted to exclude "Farms" and "Private households."</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mohun_2013, Appendix; full_transcription.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>methodology_description</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Working class unproductive labor = unproductive workers who are members of the working class (i.e., whose work is controlled by others, who have no supervisory responsibilities above shop-floor level). Defined by location in the circuit of capital: these workers are involved in M→C or C'→M' transformations (purchasing inputs, selling outputs, financial, commercial, legal, business service activities) but are NOT supervisors. Identified via the BLS CES production worker / nonsupervisory worker criterion: the CES ratio of production workers to all workers is applied to NIPA full-time equivalents by sector, yielding working class employment. Unproductive working class = working class total minus productive working class.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mohun_2013, Section 3 and Appendix; full_transcription.md</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>empirical_values</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unproductive working-class employment (Lu_wc), 1964-2010. Derived as Mohun total unproductive Lu × 0.813 (stable working class share). Employment share rises from 25.1% (1964) to 30.0% (2007). Value-added absorption share flat at 12.8% throughout — no burden increase. Units: thousands of FTEs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>Unproductive working class employment share of total employment: 1964 = 25.1%; peak 2007 = 30.0%; 2010 = ~29%. Trend: increased by about a fifth over 47 years. Unproductive working class wage share of total wages: 1964 = 18.6%; fell to 16.7% by 1992; rose back to 18.1% by 2010. Key finding: unlike total unproductive employment (which rose), the unproductive working class WAGE share is approximately flat and considerably lower than the employment share — a completely different pattern from supervisory wages.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mohun_2013, Section 4.1, Fig 2; full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>burden_finding</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Critical empirical finding: the unproductive working class absorbed 12.9% of money value added in 1964 and still 12.9% in 2010. Mean = 12.8%, standard deviation = 0.34 percentage points. Mohun concludes: 'Hence the burden to accumulation posed by the unproductive working class did not change over the whole period of 46 years.' This directly contradicts the received view (Moseley 1991, Paitaridis and Tsoulfidis 2012) that rising unproductive labor constitutes a growing burden on accumulation.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mohun_2013, Section 5, Fig 4; full_transcription.md</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>class_composition</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Working class = ~81.3% of employed population (average 1964-2010, standard deviation 0.88). Supervisors (managers-plus-capitalists) = ~18.7% of employed population. Class proportions remained remarkably stable over the 47-year period. The working class is divided into productive and unproductive components by location in the circuit of capital. Unproductive working class employment = ~25.1-30% of total employment; productive working class = ~52-58% of total employment.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mohun_2013, Section 3; full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>construction_note</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Series registry construction: step 1 op=derive, formula='Lu × 0.813', inputs=['Mohun Lu'], output='ES1501-COMBINED'. This reflects the stable 81.3% working class share of total unproductive employment. Units: thousands of full-time equivalent employees. Period 1964-2010.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Series registry ES1501; Mohun_2013, Section 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>data_sources</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Primary data: BLS CES (Current Employment Statistics, both NAICS-based 1998-2010 and discontinued SIC-based 1964-1997); NIPA (BEA). Construction follows Shaikh and Tonak (1994) as revised by Mohun (2005). Working class employment: CES production worker ratio applied to NIPA ftes. Supervisory employment and wages: computed by subtraction (NIPA totals minus working class totals), which allocates all wages missing from CES — including stock options, bonuses, retroactive pay — to supervisory workers.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mohun_2013, Appendix; full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Unproductive working-class employment (Lu_wc), 1964-2010. Derived as Mohun total unproductive Lu × 0.813 (stable working class share). Employment share rises from 25.1% (1964) to 30.0% (2007). Value-added absorption share flat at 12.8% throughout — no burden increase. Units: thousands of FTEs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>CES production worker criterion has coverage issues in Mining, Manufacturing, and Construction — 'supervisory workers' in these sectors include some non-supervisors, understating working class totals</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BLS proposed discontinuing production/non-supervisory series in 2004 (Federal Register 2005), citing classification difficulties; series was retained, but respondent difficulty may affect trend reliability</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SIC-to-NAICS transition at 1998 handled by separate tables (Table 2 for SIC, Table 3 for NAICS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ES1502</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1403,7 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ES1503</t>
+          <t>CES production worker criterion has coverage issues in Mining, Manufacturing, and Construction — 'supervisory workers' in these sectors include some non-supervisors, understating working class totals</t>
         </is>
       </c>
     </row>
@@ -1312,49 +1411,89 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ES1504</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+          <t>BLS proposed discontinuing production/non-supervisory series in 2004 (Federal Register 2005), citing classification difficulties; series was retained, but respondent difficulty may affect trend reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SIC-to-NAICS transition at 1998 handled by separate tables (Table 2 for SIC, Table 3 for NAICS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ES1502</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ES1503</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ES1504</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Mohun_2013</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Mohun, Simon. 2013 [pub. 2014]. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379. DOI: 10.1177/0486613413506080.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Mohun_2005</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Mohun, Simon. 2005. 'On measuring the wealth of nations: the US economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815. DOI: 10.1093/cje/bei043.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1371,7 +1510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1429,7 +1568,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lu Ã— 0.813</t>
+          <t>Lu — 0.813</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1581,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1602,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1948": 6426.4746}</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1626,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dollar_series</t>
+          <t>level_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>level_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10.0</t>
         </is>
       </c>
     </row>
